--- a/datos/2025-11-09-desv-rend.xlsx
+++ b/datos/2025-11-09-desv-rend.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34bf2af71bbc2e43/Documentos/GitHub/master-queseria/website/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="121" documentId="8_{A9B41A3E-D097-431F-BDF8-337D8481751A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E07CE981-E1FD-431C-B0BC-7885BB44EC87}"/>
+  <xr:revisionPtr revIDLastSave="186" documentId="8_{A9B41A3E-D097-431F-BDF8-337D8481751A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B87C588-27DE-43F9-8A53-46AB7D5D6CBB}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{2AD436DA-032C-4AC4-9751-EDA9BA4B7DA8}"/>
+    <workbookView xWindow="12420" yWindow="900" windowWidth="15390" windowHeight="14250" activeTab="1" xr2:uid="{2AD436DA-032C-4AC4-9751-EDA9BA4B7DA8}"/>
   </bookViews>
   <sheets>
     <sheet name="Desviaciones" sheetId="1" r:id="rId1"/>
+    <sheet name="Desviaciones analiticas" sheetId="2" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
     <externalReference r:id="rId4"/>
     <externalReference r:id="rId5"/>
@@ -29,22 +29,23 @@
   <definedNames>
     <definedName name="__123Graph_AGRAFIND" hidden="1">#REF!</definedName>
     <definedName name="__123Graph_AGRAFTOT" hidden="1">#REF!</definedName>
-    <definedName name="__123Graph_APRINCIPALE" hidden="1">[2]ACTIVITE!#REF!</definedName>
+    <definedName name="__123Graph_APRINCIPALE" hidden="1">[1]ACTIVITE!#REF!</definedName>
     <definedName name="__123Graph_BGRAFIND" hidden="1">#REF!</definedName>
     <definedName name="__123Graph_BGRAFTOT" hidden="1">#REF!</definedName>
-    <definedName name="__123Graph_BPRINCIPALE" hidden="1">[2]ACTIVITE!#REF!</definedName>
-    <definedName name="__123Graph_CPRINCIPALE" hidden="1">[2]ACTIVITE!#REF!</definedName>
-    <definedName name="__123Graph_XPRINCIPALE" hidden="1">[2]ACTIVITE!#REF!</definedName>
-    <definedName name="__Amount_for_Gross_Profit_Monthly_ASDA_All_Unit_2" hidden="1">[3]pcQueryData!#REF!</definedName>
+    <definedName name="__123Graph_BPRINCIPALE" hidden="1">[1]ACTIVITE!#REF!</definedName>
+    <definedName name="__123Graph_CPRINCIPALE" hidden="1">[1]ACTIVITE!#REF!</definedName>
+    <definedName name="__123Graph_XPRINCIPALE" hidden="1">[1]ACTIVITE!#REF!</definedName>
+    <definedName name="__Amount_for_Gross_Profit_Monthly_ASDA_All_Unit_2" hidden="1">[2]pcQueryData!#REF!</definedName>
     <definedName name="__Amount_for_Gross_Profit_Monthly_TESCO_All_1" hidden="1">#REF!</definedName>
-    <definedName name="__Amount_for_Monthly_1" hidden="1">[4]pcQueryData!$A$4</definedName>
+    <definedName name="__Amount_for_Monthly_1" hidden="1">[3]pcQueryData!$A$4</definedName>
     <definedName name="__c" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="__c" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="__c" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="_100_PV">#REF!</definedName>
     <definedName name="_100_SVI">#REF!</definedName>
     <definedName name="_1000_XM">#REF!</definedName>
     <definedName name="_145110">#REF!</definedName>
-    <definedName name="_162460">[5]STEPHAN!$B$2:$P$71</definedName>
+    <definedName name="_162460">[4]STEPHAN!$B$2:$P$71</definedName>
     <definedName name="_170_LIGHT">#REF!</definedName>
     <definedName name="_170_PV">#REF!</definedName>
     <definedName name="_171015">#REF!</definedName>
@@ -57,10 +58,10 @@
     <definedName name="_172020">#REF!</definedName>
     <definedName name="_172022">#REF!</definedName>
     <definedName name="_172062">#REF!</definedName>
-    <definedName name="_172510">[5]STEPHAN!$B$2:$Q$71</definedName>
-    <definedName name="_172610">[5]STEPHAN!$B$2:$Q$71</definedName>
+    <definedName name="_172510">[4]STEPHAN!$B$2:$Q$71</definedName>
+    <definedName name="_172610">[4]STEPHAN!$B$2:$Q$71</definedName>
     <definedName name="_176072">#REF!</definedName>
-    <definedName name="_Amount_for_Monthly" hidden="1">[6]pcQueryData!$A$3</definedName>
+    <definedName name="_Amount_for_Monthly" hidden="1">[5]pcQueryData!$A$3</definedName>
     <definedName name="_Fill" hidden="1">#REF!</definedName>
     <definedName name="_Key1" hidden="1">#REF!</definedName>
     <definedName name="_Key2" hidden="1">#REF!</definedName>
@@ -79,13 +80,13 @@
     <definedName name="_pcSlicerSheet12_Slicer3" hidden="1">#REF!</definedName>
     <definedName name="_pcSlicerSheet13_Slicer2" hidden="1">#REF!</definedName>
     <definedName name="_pcSlicerSheet13_Slicer3" hidden="1">#REF!</definedName>
-    <definedName name="_pcSlicerSheet14_Slicer1" hidden="1">[3]_pcSlicerSheet14!$A$2:$A$25</definedName>
+    <definedName name="_pcSlicerSheet14_Slicer1" hidden="1">[2]_pcSlicerSheet14!$A$2:$A$25</definedName>
     <definedName name="_pcSlicerSheet14_Slicer2" hidden="1">#REF!</definedName>
     <definedName name="_pcSlicerSheet14_Slicer3" hidden="1">#REF!</definedName>
-    <definedName name="_pcSlicerSheet15_Slicer1" hidden="1">[3]_pcSlicerSheet15!$A$2:$A$25</definedName>
+    <definedName name="_pcSlicerSheet15_Slicer1" hidden="1">[2]_pcSlicerSheet15!$A$2:$A$25</definedName>
     <definedName name="_pcSlicerSheet15_Slicer2" hidden="1">#REF!</definedName>
     <definedName name="_pcSlicerSheet15_Slicer3" hidden="1">#REF!</definedName>
-    <definedName name="_pcSlicerSheet16_Slicer1" hidden="1">[3]_pcSlicerSheet16!$A$2:$A$25</definedName>
+    <definedName name="_pcSlicerSheet16_Slicer1" hidden="1">[2]_pcSlicerSheet16!$A$2:$A$25</definedName>
     <definedName name="_pcSlicerSheet16_Slicer2" hidden="1">#REF!</definedName>
     <definedName name="_pcSlicerSheet16_Slicer3" hidden="1">#REF!</definedName>
     <definedName name="_pcSlicerSheet17_Slicer1" hidden="1">#REF!</definedName>
@@ -130,7 +131,7 @@
     <definedName name="_pcSlicerSheet37_Slicer1" hidden="1">#REF!</definedName>
     <definedName name="_pcSlicerSheet38_Slicer1" hidden="1">#REF!</definedName>
     <definedName name="_pcSlicerSheet39_Slicer1" hidden="1">#REF!</definedName>
-    <definedName name="_pcSlicerSheet4_Slicer1" hidden="1">[3]_pcSlicerSheet4!$A$2:$A$14</definedName>
+    <definedName name="_pcSlicerSheet4_Slicer1" hidden="1">[2]_pcSlicerSheet4!$A$2:$A$14</definedName>
     <definedName name="_pcSlicerSheet4_Slicer2" hidden="1">#REF!</definedName>
     <definedName name="_pcSlicerSheet40_Slicer1" hidden="1">#REF!</definedName>
     <definedName name="_pcSlicerSheet41_Slicer1" hidden="1">#REF!</definedName>
@@ -166,112 +167,162 @@
     <definedName name="_pcSlicerSheet9_Slicer1" hidden="1">#REF!</definedName>
     <definedName name="_Sort" hidden="1">#REF!</definedName>
     <definedName name="a" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="a" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="a" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="A_impresión_IM">#REF!</definedName>
     <definedName name="aaa" hidden="1">#REF!</definedName>
     <definedName name="aaaa" hidden="1">#REF!</definedName>
     <definedName name="aaaaa" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="aaaaa" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="aaaaa" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="aaaaaaaaaaaaaaaa" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="aaaaaaaaaaaaaaaa" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="aaaaaaaaaaaaaaaa" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="AASAS" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="AASAS" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="AASAS" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ADV" localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"ANALYSE";#N/A,#N/A,TRUE,"PM VOLUME";#N/A,#N/A,TRUE,"PM VALEUR";#N/A,#N/A,TRUE,"AR1";#N/A,#N/A,TRUE,"AR2";#N/A,#N/A,TRUE,"RAF";#N/A,#N/A,TRUE,"BILAN";#N/A,#N/A,TRUE,"CASH FLOW";#N/A,#N/A,TRUE,"ETAT FI"}</definedName>
+    <definedName name="ADV" localSheetId="1" hidden="1">{#N/A,#N/A,TRUE,"ANALYSE";#N/A,#N/A,TRUE,"PM VOLUME";#N/A,#N/A,TRUE,"PM VALEUR";#N/A,#N/A,TRUE,"AR1";#N/A,#N/A,TRUE,"AR2";#N/A,#N/A,TRUE,"RAF";#N/A,#N/A,TRUE,"BILAN";#N/A,#N/A,TRUE,"CASH FLOW";#N/A,#N/A,TRUE,"ETAT FI"}</definedName>
     <definedName name="ADV" hidden="1">{#N/A,#N/A,TRUE,"ANALYSE";#N/A,#N/A,TRUE,"PM VOLUME";#N/A,#N/A,TRUE,"PM VALEUR";#N/A,#N/A,TRUE,"AR1";#N/A,#N/A,TRUE,"AR2";#N/A,#N/A,TRUE,"RAF";#N/A,#N/A,TRUE,"BILAN";#N/A,#N/A,TRUE,"CASH FLOW";#N/A,#N/A,TRUE,"ETAT FI"}</definedName>
     <definedName name="ana" localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"EC COMM-t";#N/A,#N/A,TRUE,"EC PAR PDTS-t";#N/A,#N/A,TRUE,"EC MAT-t";#N/A,#N/A,TRUE,"SUIVI HAUSSES-t"}</definedName>
+    <definedName name="ana" localSheetId="1" hidden="1">{#N/A,#N/A,TRUE,"EC COMM-t";#N/A,#N/A,TRUE,"EC PAR PDTS-t";#N/A,#N/A,TRUE,"EC MAT-t";#N/A,#N/A,TRUE,"SUIVI HAUSSES-t"}</definedName>
     <definedName name="ana" hidden="1">{#N/A,#N/A,TRUE,"EC COMM-t";#N/A,#N/A,TRUE,"EC PAR PDTS-t";#N/A,#N/A,TRUE,"EC MAT-t";#N/A,#N/A,TRUE,"SUIVI HAUSSES-t"}</definedName>
     <definedName name="anscount" hidden="1">1</definedName>
     <definedName name="ardqer" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="ardqer" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ardqer" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ASD" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="ASD" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ASD" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ASDF" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="ASDF" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ASDF" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="asdfas" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="asdfas" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="asdfas" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="aùsw" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="aùsw" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="aùsw" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="bbbbb" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge"}</definedName>
+    <definedName name="bbbbb" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge"}</definedName>
     <definedName name="bbbbb" hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge"}</definedName>
     <definedName name="bd">#REF!</definedName>
     <definedName name="bimes" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge";#N/A,#N/A,FALSE,"cumul I";#N/A,#N/A,FALSE,"cumul II";#N/A,#N/A,FALSE,"cumul III"}</definedName>
+    <definedName name="bimes" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge";#N/A,#N/A,FALSE,"cumul I";#N/A,#N/A,FALSE,"cumul II";#N/A,#N/A,FALSE,"cumul III"}</definedName>
     <definedName name="bimes" hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge";#N/A,#N/A,FALSE,"cumul I";#N/A,#N/A,FALSE,"cumul II";#N/A,#N/A,FALSE,"cumul III"}</definedName>
     <definedName name="bof">"ComboBox1"</definedName>
     <definedName name="byikbyuj" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="byikbyuj" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="byikbyuj" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="byubtyuj" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="byubtyuj" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="byubtyuj" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="byukkty" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="byukkty" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="byukkty" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="byuku" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="byuku" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="byuku" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="č" localSheetId="0" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
+    <definedName name="č" localSheetId="1" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="č" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="cc" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="cc" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="cc" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ccc" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="ccc" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ccc" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="cccc" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="cccc" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="cccc" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="CCSFDFRDF" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="CCSFDFRDF" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="CCSFDFRDF" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="cdf" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="cdf" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="cdf" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="CDVF" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="CDVF" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="CDVF" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="copie" localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"ANALYSE";#N/A,#N/A,TRUE,"PM VOLUME";#N/A,#N/A,TRUE,"PM VALEUR";#N/A,#N/A,TRUE,"AR1";#N/A,#N/A,TRUE,"AR2";#N/A,#N/A,TRUE,"RAF";#N/A,#N/A,TRUE,"BILAN";#N/A,#N/A,TRUE,"CASH FLOW";#N/A,#N/A,TRUE,"ETAT FI"}</definedName>
+    <definedName name="copie" localSheetId="1" hidden="1">{#N/A,#N/A,TRUE,"ANALYSE";#N/A,#N/A,TRUE,"PM VOLUME";#N/A,#N/A,TRUE,"PM VALEUR";#N/A,#N/A,TRUE,"AR1";#N/A,#N/A,TRUE,"AR2";#N/A,#N/A,TRUE,"RAF";#N/A,#N/A,TRUE,"BILAN";#N/A,#N/A,TRUE,"CASH FLOW";#N/A,#N/A,TRUE,"ETAT FI"}</definedName>
     <definedName name="copie" hidden="1">{#N/A,#N/A,TRUE,"ANALYSE";#N/A,#N/A,TRUE,"PM VOLUME";#N/A,#N/A,TRUE,"PM VALEUR";#N/A,#N/A,TRUE,"AR1";#N/A,#N/A,TRUE,"AR2";#N/A,#N/A,TRUE,"RAF";#N/A,#N/A,TRUE,"BILAN";#N/A,#N/A,TRUE,"CASH FLOW";#N/A,#N/A,TRUE,"ETAT FI"}</definedName>
     <definedName name="D" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="D" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="D" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="DAFreofè0eirfh" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="DAFreofè0eirfh" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="DAFreofè0eirfh" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="dd">#REF!</definedName>
     <definedName name="DDD" localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"EC COMM-t";#N/A,#N/A,TRUE,"EC PAR PDTS-t";#N/A,#N/A,TRUE,"EC MAT-t";#N/A,#N/A,TRUE,"SUIVI HAUSSES-t"}</definedName>
+    <definedName name="DDD" localSheetId="1" hidden="1">{#N/A,#N/A,TRUE,"EC COMM-t";#N/A,#N/A,TRUE,"EC PAR PDTS-t";#N/A,#N/A,TRUE,"EC MAT-t";#N/A,#N/A,TRUE,"SUIVI HAUSSES-t"}</definedName>
     <definedName name="DDD" hidden="1">{#N/A,#N/A,TRUE,"EC COMM-t";#N/A,#N/A,TRUE,"EC PAR PDTS-t";#N/A,#N/A,TRUE,"EC MAT-t";#N/A,#N/A,TRUE,"SUIVI HAUSSES-t"}</definedName>
     <definedName name="DDDDD" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="DDDDD" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="DDDDD" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ddddddd" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="ddddddd" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ddddddd" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ddjdjdj" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="ddjdjdj" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ddjdjdj" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="dfa" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="dfa" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="dfa" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="DFda" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="DFda" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="DFda" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="DFRSFG" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="DFRSFG" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="DFRSFG" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="djdjdjd" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="djdjdjd" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="djdjdjd" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="dqdqdqd" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="dqdqdqd" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="dqdqdqd" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="DRAGAN" localSheetId="0" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
+    <definedName name="DRAGAN" localSheetId="1" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="DRAGAN" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="draganć" localSheetId="0" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
+    <definedName name="draganć" localSheetId="1" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="draganć" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="DSFSDGFG" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="DSFSDGFG" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="DSFSDGFG" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="dthrrr" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="dthrrr" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="dthrrr" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ECA" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ANALYSE";#N/A,#N/A,FALSE,"PM VALEUR"}</definedName>
+    <definedName name="ECA" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ANALYSE";#N/A,#N/A,FALSE,"PM VALEUR"}</definedName>
     <definedName name="ECA" hidden="1">{#N/A,#N/A,FALSE,"ANALYSE";#N/A,#N/A,FALSE,"PM VALEUR"}</definedName>
     <definedName name="ECARTBM" localSheetId="0" hidden="1">{"DETAIL",#N/A,FALSE,"REELBUDGET";"TOTAL",#N/A,FALSE,"REELBUDGET"}</definedName>
+    <definedName name="ECARTBM" localSheetId="1" hidden="1">{"DETAIL",#N/A,FALSE,"REELBUDGET";"TOTAL",#N/A,FALSE,"REELBUDGET"}</definedName>
     <definedName name="ECARTBM" hidden="1">{"DETAIL",#N/A,FALSE,"REELBUDGET";"TOTAL",#N/A,FALSE,"REELBUDGET"}</definedName>
     <definedName name="eeeee" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="eeeee" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="eeeee" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="eerreerr" hidden="1">#REF!</definedName>
     <definedName name="efazefze" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="efazefze" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="efazefze" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ehethrer" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="ehethrer" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ehethrer" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ere" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="ere" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ere" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ertetq" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="ertetq" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ertetq" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ertetqe" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="ertetqe" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ertetqe" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ertwert" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="ertwert" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ertwert" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ertwet" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="ertwet" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ertwet" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="EssLatest">"JAN"</definedName>
     <definedName name="EssLatest_10">"JAN"</definedName>
@@ -326,84 +377,122 @@
     <definedName name="ExactAddinConnection.900" hidden="1">"SRVSQLCZ;900;skubistova;1"</definedName>
     <definedName name="ExactAddinReports" hidden="1">1</definedName>
     <definedName name="EXCEL" localSheetId="0" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
+    <definedName name="EXCEL" localSheetId="1" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="EXCEL" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="ezfzef" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="ezfzef" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ezfzef" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="fazefzef" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="fazefzef" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="fazefzef" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="FDDSFDSGF" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="FDDSFDSGF" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="FDDSFDSGF" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="fdsdsgfsggd" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"DIVISION";#N/A,#N/A,FALSE,"ED CAT";#N/A,#N/A,FALSE,"ED CAREL";#N/A,#N/A,FALSE,"ED JORT";#N/A,#N/A,FALSE,"ED VEYS";#N/A,#N/A,FALSE,"ED ORBEC";#N/A,#N/A,FALSE,"ED CLECY"}</definedName>
+    <definedName name="fdsdsgfsggd" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"DIVISION";#N/A,#N/A,FALSE,"ED CAT";#N/A,#N/A,FALSE,"ED CAREL";#N/A,#N/A,FALSE,"ED JORT";#N/A,#N/A,FALSE,"ED VEYS";#N/A,#N/A,FALSE,"ED ORBEC";#N/A,#N/A,FALSE,"ED CLECY"}</definedName>
     <definedName name="fdsdsgfsggd" hidden="1">{#N/A,#N/A,FALSE,"DIVISION";#N/A,#N/A,FALSE,"ED CAT";#N/A,#N/A,FALSE,"ED CAREL";#N/A,#N/A,FALSE,"ED JORT";#N/A,#N/A,FALSE,"ED VEYS";#N/A,#N/A,FALSE,"ED ORBEC";#N/A,#N/A,FALSE,"ED CLECY"}</definedName>
     <definedName name="fdzfzefzef" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="fdzfzefzef" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="fdzfzefzef" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="feazefzaef" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="feazefzaef" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="feazefzaef" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="fere" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="fere" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="fere" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ferw" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="ferw" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ferw" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ffff" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="ffff" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ffff" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ffffffffff" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="ffffffffff" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ffffffffff" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="fg" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="fg" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="fg" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="fgffg" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="fgffg" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="fgffg" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="FSDG" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="FSDG" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="FSDG" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="fterearez" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="fterearez" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="fterearez" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="fzfzfef" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="fzfzfef" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="fzfzfef" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="GBP">'[7]Nrj présentat°'!$AR$2</definedName>
+    <definedName name="GBP">'[6]Nrj présentat°'!$AR$2</definedName>
     <definedName name="gegege" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="gegege" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gegege" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="GF" hidden="1">[8]ACTIVITE!#REF!</definedName>
+    <definedName name="GF" hidden="1">[7]ACTIVITE!#REF!</definedName>
     <definedName name="gfhkkmh" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="gfhkkmh" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="gfhkkmh" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="GG" hidden="1">[8]ACTIVITE!#REF!</definedName>
+    <definedName name="GG" hidden="1">[7]ACTIVITE!#REF!</definedName>
     <definedName name="GGGG" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="GGGG" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="GGGG" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ggggg" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="ggggg" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ggggg" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ggggggggggg" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="ggggggggggg" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ggggggggggg" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="GHJ" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="GHJ" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="GHJ" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="gsdgsd" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="gsdgsd" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gsdgsd" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gtrgtrg" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="gtrgtrg" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gtrgtrg" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gtrztrgr" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="gtrztrgr" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gtrztrgr" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gzgtzgz" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="gzgtzgz" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gzgtzgz" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gzgzgz" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="gzgzgz" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gzgzgz" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gzgzgzgt" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="gzgzgzgt" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gzgzgzgt" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gztgrtrg" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="gztgrtrg" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gztgrtrg" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gztgzgt" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="gztgzgt" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gztgzgt" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="hbhajx" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="hbhajx" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="hbhajx" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="hfderfPOURE" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="hfderfPOURE" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="hfderfPOURE" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="hfhfth" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="hfhfth" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="hfhfth" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="hg" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="hg" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="hg" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="hhfxhxfh" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="hhfxhxfh" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="hhfxhxfh" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="hhhh" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="hhhh" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="hhhh" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="hhhhhhh" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="hhhhhhh" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="hhhhhhh" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="HTML_CodePage" hidden="1">1250</definedName>
     <definedName name="HTML_Control" localSheetId="0" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
+    <definedName name="HTML_Control" localSheetId="1" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="HTML_Control" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="HTML_Description" hidden="1">""</definedName>
     <definedName name="HTML_Email" hidden="1">""</definedName>
@@ -418,299 +507,437 @@
     <definedName name="HTML_PathFile" hidden="1">"C:\My Documents\MyHTML.htm"</definedName>
     <definedName name="HTML_Title" hidden="1">"Moja PRODAJA  II VELJAČA '2001"</definedName>
     <definedName name="hzthzhr" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="hzthzhr" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="hzthzhr" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="iiiiii" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="iiiiii" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="iiiiii" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="iiiiiiii" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="iiiiiiii" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="iiiiiiii" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="IRI_WorkspaceId" hidden="1">"bc7b7ef8a7ba454b9c6b30466fcd76e0"</definedName>
     <definedName name="ITAPLASPIC">#REF!</definedName>
     <definedName name="IZVQ01" localSheetId="0" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
+    <definedName name="IZVQ01" localSheetId="1" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="IZVQ01" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="j" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="j" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="j" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="jcjfjfjjf" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="jcjfjfjjf" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="jcjfjfjjf" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="jdjdjdj" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="jdjdjdj" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="jdjdjdj" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="jej" localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"EC COMM-t";#N/A,#N/A,TRUE,"EC PAR PDTS-t";#N/A,#N/A,TRUE,"EC MAT-t";#N/A,#N/A,TRUE,"SUIVI HAUSSES-t"}</definedName>
+    <definedName name="jej" localSheetId="1" hidden="1">{#N/A,#N/A,TRUE,"EC COMM-t";#N/A,#N/A,TRUE,"EC PAR PDTS-t";#N/A,#N/A,TRUE,"EC MAT-t";#N/A,#N/A,TRUE,"SUIVI HAUSSES-t"}</definedName>
     <definedName name="jej" hidden="1">{#N/A,#N/A,TRUE,"EC COMM-t";#N/A,#N/A,TRUE,"EC PAR PDTS-t";#N/A,#N/A,TRUE,"EC MAT-t";#N/A,#N/A,TRUE,"SUIVI HAUSSES-t"}</definedName>
     <definedName name="jjfhfh" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="jjfhfh" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="jjfhfh" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="jjj" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="jjj" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="jjj" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="jjjjj" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="jjjjj" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="jjjjj" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="kfkfkfk" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="kfkfkfk" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="kfkfkfk" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="kfkfkfkfkkf" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="kfkfkfkfkkf" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="kfkfkfkfkkf" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="khkhkhk" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="khkhkhk" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="khkhkhk" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="khkk" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="khkk" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="khkk" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="kirirtir" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="kirirtir" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="kirirtir" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="kjfsoyiupo6rhtgz" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="kjfsoyiupo6rhtgz" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="kjfsoyiupo6rhtgz" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="kjhjhkjh" localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"VOLUMES";#N/A,#N/A,TRUE,"RDT CAM";#N/A,#N/A,TRUE,"RDT BDP";#N/A,#N/A,TRUE,"RDT LIV250";#N/A,#N/A,TRUE,"RDT LIV500";#N/A,#N/A,TRUE,"ING CAM";#N/A,#N/A,TRUE,"ING BDP";#N/A,#N/A,TRUE,"ING LIV";#N/A,#N/A,TRUE,"CHARGES";#N/A,#N/A,TRUE,"ENERGIES";#N/A,#N/A,TRUE,"PRODCHIM";#N/A,#N/A,TRUE,"EFFECTIF";#N/A,#N/A,TRUE,"PRIX CESSION";#N/A,#N/A,TRUE,"CPTE EXPLOIT";#N/A,#N/A,TRUE,"CONTROLE"}</definedName>
+    <definedName name="kjhjhkjh" localSheetId="1" hidden="1">{#N/A,#N/A,TRUE,"VOLUMES";#N/A,#N/A,TRUE,"RDT CAM";#N/A,#N/A,TRUE,"RDT BDP";#N/A,#N/A,TRUE,"RDT LIV250";#N/A,#N/A,TRUE,"RDT LIV500";#N/A,#N/A,TRUE,"ING CAM";#N/A,#N/A,TRUE,"ING BDP";#N/A,#N/A,TRUE,"ING LIV";#N/A,#N/A,TRUE,"CHARGES";#N/A,#N/A,TRUE,"ENERGIES";#N/A,#N/A,TRUE,"PRODCHIM";#N/A,#N/A,TRUE,"EFFECTIF";#N/A,#N/A,TRUE,"PRIX CESSION";#N/A,#N/A,TRUE,"CPTE EXPLOIT";#N/A,#N/A,TRUE,"CONTROLE"}</definedName>
     <definedName name="kjhjhkjh" hidden="1">{#N/A,#N/A,TRUE,"VOLUMES";#N/A,#N/A,TRUE,"RDT CAM";#N/A,#N/A,TRUE,"RDT BDP";#N/A,#N/A,TRUE,"RDT LIV250";#N/A,#N/A,TRUE,"RDT LIV500";#N/A,#N/A,TRUE,"ING CAM";#N/A,#N/A,TRUE,"ING BDP";#N/A,#N/A,TRUE,"ING LIV";#N/A,#N/A,TRUE,"CHARGES";#N/A,#N/A,TRUE,"ENERGIES";#N/A,#N/A,TRUE,"PRODCHIM";#N/A,#N/A,TRUE,"EFFECTIF";#N/A,#N/A,TRUE,"PRIX CESSION";#N/A,#N/A,TRUE,"CPTE EXPLOIT";#N/A,#N/A,TRUE,"CONTROLE"}</definedName>
     <definedName name="kk" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="kk" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="kk" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="kkkkk" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="kkkkk" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="kkkkk" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="LLL" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="LLL" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="LLL" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="m" localSheetId="0" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
+    <definedName name="m" localSheetId="1" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="m" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="MARTESANA">#REF!</definedName>
     <definedName name="minnii" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="minnii" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="minnii" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="MOIS">[9]Grille!$B$3:$C$14</definedName>
+    <definedName name="MOIS">[8]Grille!$B$3:$C$14</definedName>
     <definedName name="Month_No.">7</definedName>
     <definedName name="nico" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="nico" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="nico" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="NUEVA" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="NUEVA" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="NUEVA" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="nueva1" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="nueva1" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="nueva1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ñ" hidden="1">#REF!</definedName>
     <definedName name="ño" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="ño" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ño" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ODRŽ." localSheetId="0" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
+    <definedName name="ODRŽ." localSheetId="1" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="ODRŽ." hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="òflfgfppfpf" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="òflfgfppfpf" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="òflfgfppfpf" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="OIOIIUIUG" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="OIOIIUIUG" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="OIOIIUIUG" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ooo" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="ooo" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ooo" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="oooooo" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="oooooo" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="oooooo" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="P_HostName">#REF!</definedName>
     <definedName name="P_ServerName">#REF!</definedName>
     <definedName name="pippo" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="pippo" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="pippo" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="pluto" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="pluto" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="pluto" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="PO" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="PO" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="PO" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="poùH" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="poùH" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="poùH" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ppp" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="ppp" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ppp" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="PROD." localSheetId="0" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
+    <definedName name="PROD." localSheetId="1" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="PROD." hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="prw" localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"VOLUMES";#N/A,#N/A,TRUE,"1A-TB 240";#N/A,#N/A,TRUE,"1B-TB 250";#N/A,#N/A,TRUE,"1D-Tr 240";#N/A,#N/A,TRUE,"1E-Tr 250";#N/A,#N/A,TRUE,"1M-Tr 250 60%";#N/A,#N/A,TRUE,"5A-Cru 240";#N/A,#N/A,TRUE,"5B-Cru 250";#N/A,#N/A,TRUE,"5D-Bio 250";#N/A,#N/A,TRUE,"3B-TB 320";#N/A,#N/A,TRUE,"3C-TB 350";#N/A,#N/A,TRUE,"Sérum";#N/A,#N/A,TRUE,"Recap Mat";#N/A,#N/A,TRUE,"ING CAM-TB";#N/A,#N/A,TRUE,"ING CAM-60%";#N/A,#N/A,TRUE,"ING CAM-Cru";#N/A,#N/A,TRUE,"ING COULO -52%";#N/A,#N/A,TRUE,"Recap Ing";#N/A,#N/A,TRUE,"CHARGES";#N/A,#N/A,TRUE,"Répart_charges";#N/A,#N/A,TRUE,"ENERGIES";#N/A,#N/A,TRUE,"EFFECTIF";#N/A,#N/A,TRUE,"Synthèse";#N/A,#N/A,TRUE,"CPTE EXPLOIT";#N/A,#N/A,TRUE,"PRIX CESSION";#N/A,#N/A,TRUE,"CONTROLE"}</definedName>
+    <definedName name="prw" localSheetId="1" hidden="1">{#N/A,#N/A,TRUE,"VOLUMES";#N/A,#N/A,TRUE,"1A-TB 240";#N/A,#N/A,TRUE,"1B-TB 250";#N/A,#N/A,TRUE,"1D-Tr 240";#N/A,#N/A,TRUE,"1E-Tr 250";#N/A,#N/A,TRUE,"1M-Tr 250 60%";#N/A,#N/A,TRUE,"5A-Cru 240";#N/A,#N/A,TRUE,"5B-Cru 250";#N/A,#N/A,TRUE,"5D-Bio 250";#N/A,#N/A,TRUE,"3B-TB 320";#N/A,#N/A,TRUE,"3C-TB 350";#N/A,#N/A,TRUE,"Sérum";#N/A,#N/A,TRUE,"Recap Mat";#N/A,#N/A,TRUE,"ING CAM-TB";#N/A,#N/A,TRUE,"ING CAM-60%";#N/A,#N/A,TRUE,"ING CAM-Cru";#N/A,#N/A,TRUE,"ING COULO -52%";#N/A,#N/A,TRUE,"Recap Ing";#N/A,#N/A,TRUE,"CHARGES";#N/A,#N/A,TRUE,"Répart_charges";#N/A,#N/A,TRUE,"ENERGIES";#N/A,#N/A,TRUE,"EFFECTIF";#N/A,#N/A,TRUE,"Synthèse";#N/A,#N/A,TRUE,"CPTE EXPLOIT";#N/A,#N/A,TRUE,"PRIX CESSION";#N/A,#N/A,TRUE,"CONTROLE"}</definedName>
     <definedName name="prw" hidden="1">{#N/A,#N/A,TRUE,"VOLUMES";#N/A,#N/A,TRUE,"1A-TB 240";#N/A,#N/A,TRUE,"1B-TB 250";#N/A,#N/A,TRUE,"1D-Tr 240";#N/A,#N/A,TRUE,"1E-Tr 250";#N/A,#N/A,TRUE,"1M-Tr 250 60%";#N/A,#N/A,TRUE,"5A-Cru 240";#N/A,#N/A,TRUE,"5B-Cru 250";#N/A,#N/A,TRUE,"5D-Bio 250";#N/A,#N/A,TRUE,"3B-TB 320";#N/A,#N/A,TRUE,"3C-TB 350";#N/A,#N/A,TRUE,"Sérum";#N/A,#N/A,TRUE,"Recap Mat";#N/A,#N/A,TRUE,"ING CAM-TB";#N/A,#N/A,TRUE,"ING CAM-60%";#N/A,#N/A,TRUE,"ING CAM-Cru";#N/A,#N/A,TRUE,"ING COULO -52%";#N/A,#N/A,TRUE,"Recap Ing";#N/A,#N/A,TRUE,"CHARGES";#N/A,#N/A,TRUE,"Répart_charges";#N/A,#N/A,TRUE,"ENERGIES";#N/A,#N/A,TRUE,"EFFECTIF";#N/A,#N/A,TRUE,"Synthèse";#N/A,#N/A,TRUE,"CPTE EXPLOIT";#N/A,#N/A,TRUE,"PRIX CESSION";#N/A,#N/A,TRUE,"CONTROLE"}</definedName>
     <definedName name="QQQQQQQQQQQQ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="QQQQQQQQQQQQ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="QQQQQQQQQQQQ" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="qw" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="qw" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="qw" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="reter" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="reter" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="reter" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="rgeegeqg" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="rgeegeqg" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="rgeegeqg" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="rrrrrr" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="rrrrrr" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="rrrrrr" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="rteqtq" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="rteqtq" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="rteqtq" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="rtgtgrzg" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="rtgtgrzg" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="rtgtgrzg" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="rtherrh" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="rtherrh" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="rtherrh" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="rtqtr" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="rtqtr" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="rtqtr" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="rtqtrq" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="rtqtrq" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="rtqtrq" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="sa" hidden="1">#REF!</definedName>
     <definedName name="SAPBEXrevision" hidden="1">3</definedName>
     <definedName name="SAPBEXsysID" hidden="1">"BPP"</definedName>
     <definedName name="SAPBEXwbID" hidden="1">"4GNIIN8XAB6OYSDJFHQ7XQLUA"</definedName>
     <definedName name="sd" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="sd" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="sd" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="SDFDSJF" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="SDFDSJF" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="SDFDSJF" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="sdsd" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="sdsd" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="sdsd" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="SEDSDS" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="SEDSDS" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="SEDSDS" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="sencount" hidden="1">1</definedName>
     <definedName name="SSSADADSF" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="SSSADADSF" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="SSSADADSF" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ssss" hidden="1">#REF!</definedName>
     <definedName name="sssssss" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="sssssss" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="sssssss" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ssssssssssssssssssssssssss" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="ssssssssssssssssssssssssss" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ssssssssssssssssssssssssss" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="stsrhs" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="stsrhs" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="stsrhs" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="Sweden" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="Sweden" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="Sweden" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="t" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="t" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="t" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="T04CC" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="T04CC" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="T04CC" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="t79oto97t" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="t79oto97t" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="t79oto97t" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="t7u74u" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="t7u74u" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="t7u74u" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="t7u75" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="t7u75" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="t7u75" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="t7ur7u" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="t7ur7u" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="t7ur7u" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="tgfcvds" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="tgfcvds" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="tgfcvds" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="tgrgg" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="tgrgg" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="tgrgg" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="tgzgtgrrz" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="tgzgtgrrz" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="tgzgtgrrz" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="thertherth" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="thertherth" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="thertherth" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="thzsrhrzhtz" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="thzsrhrzhtz" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="thzsrhrzhtz" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="tikl679o679o" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="tikl679o679o" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="tikl679o679o" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="TM1REBUILDOPTION">0</definedName>
     <definedName name="toma" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="toma" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="toma" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="trjk5i57" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="trjk5i57" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="trjk5i57" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="tt" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="tt" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="tt" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="tttt" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="tttt" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="tttt" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="tttttt" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="tttttt" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="tttttt" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="tttttttttttt" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="tttttttttttt" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="tttttttttttt" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ttttttttttttt" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="ttttttttttttt" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ttttttttttttt" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="tyiltu9ol" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="tyiltu9ol" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="tyiltu9ol" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ugkj" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="ugkj" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ugkj" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ukkkk" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="ukkkk" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ukkkk" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="USD">'[7]Nrj présentat°'!$AR$3</definedName>
+    <definedName name="USD">'[6]Nrj présentat°'!$AR$3</definedName>
     <definedName name="uttkjg" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="uttkjg" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="uttkjg" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="uuuu" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="uuuu" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="uuuu" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="uuuuuu" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="uuuuuu" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="uuuuuu" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="v6uyjyu" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="v6uyjyu" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="v6uyjyu" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="vcbbxb" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="vcbbxb" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="vcbbxb" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="vvvv" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="vvvv" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="vvvv" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="vvvvbbbb" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="vvvvbbbb" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="vvvvbbbb" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="vvvvvv" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="vvvvvv" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="vvvvvv" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="vvvvvvvv" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="vvvvvvvv" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="vvvvvvvv" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="w" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="w" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="w" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="we" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="we" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="we" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wer" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ANALYSE";#N/A,#N/A,FALSE,"PM VALEUR"}</definedName>
+    <definedName name="wer" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ANALYSE";#N/A,#N/A,FALSE,"PM VALEUR"}</definedName>
     <definedName name="wer" hidden="1">{#N/A,#N/A,FALSE,"ANALYSE";#N/A,#N/A,FALSE,"PM VALEUR"}</definedName>
     <definedName name="wetrwrt" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="wetrwrt" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wetrwrt" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wewe" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="wewe" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wewe" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wrn.CCC." localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="wrn.CCC." localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wrn.CCC." hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wrn.Charges." localSheetId="0" hidden="1">{"Analyse charges",#N/A,FALSE,"Feuil1 (2)"}</definedName>
+    <definedName name="wrn.Charges." localSheetId="1" hidden="1">{"Analyse charges",#N/A,FALSE,"Feuil1 (2)"}</definedName>
     <definedName name="wrn.Charges." hidden="1">{"Analyse charges",#N/A,FALSE,"Feuil1 (2)"}</definedName>
     <definedName name="wrn.Charges._.Clécy." localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"Evol98";#N/A,#N/A,FALSE,"Saisie98"}</definedName>
+    <definedName name="wrn.Charges._.Clécy." localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"Evol98";#N/A,#N/A,FALSE,"Saisie98"}</definedName>
     <definedName name="wrn.Charges._.Clécy." hidden="1">{#N/A,#N/A,FALSE,"Evol98";#N/A,#N/A,FALSE,"Saisie98"}</definedName>
     <definedName name="wrn.CLECY." localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"VOLUMES";#N/A,#N/A,TRUE,"1A-TB 240";#N/A,#N/A,TRUE,"1B-TB 250";#N/A,#N/A,TRUE,"1D-Tr 240";#N/A,#N/A,TRUE,"1E-Tr 250";#N/A,#N/A,TRUE,"1M-Tr 250 60%";#N/A,#N/A,TRUE,"5A-Cru 240";#N/A,#N/A,TRUE,"5B-Cru 250";#N/A,#N/A,TRUE,"5D-Bio 250";#N/A,#N/A,TRUE,"3B-TB 320";#N/A,#N/A,TRUE,"3C-TB 350";#N/A,#N/A,TRUE,"Sérum";#N/A,#N/A,TRUE,"Recap Mat";#N/A,#N/A,TRUE,"ING CAM-TB";#N/A,#N/A,TRUE,"ING CAM-60%";#N/A,#N/A,TRUE,"ING CAM-Cru";#N/A,#N/A,TRUE,"ING COULO -52%";#N/A,#N/A,TRUE,"Recap Ing";#N/A,#N/A,TRUE,"CHARGES";#N/A,#N/A,TRUE,"Répart_charges";#N/A,#N/A,TRUE,"ENERGIES";#N/A,#N/A,TRUE,"EFFECTIF";#N/A,#N/A,TRUE,"Synthèse";#N/A,#N/A,TRUE,"CPTE EXPLOIT";#N/A,#N/A,TRUE,"PRIX CESSION";#N/A,#N/A,TRUE,"CONTROLE"}</definedName>
+    <definedName name="wrn.CLECY." localSheetId="1" hidden="1">{#N/A,#N/A,TRUE,"VOLUMES";#N/A,#N/A,TRUE,"1A-TB 240";#N/A,#N/A,TRUE,"1B-TB 250";#N/A,#N/A,TRUE,"1D-Tr 240";#N/A,#N/A,TRUE,"1E-Tr 250";#N/A,#N/A,TRUE,"1M-Tr 250 60%";#N/A,#N/A,TRUE,"5A-Cru 240";#N/A,#N/A,TRUE,"5B-Cru 250";#N/A,#N/A,TRUE,"5D-Bio 250";#N/A,#N/A,TRUE,"3B-TB 320";#N/A,#N/A,TRUE,"3C-TB 350";#N/A,#N/A,TRUE,"Sérum";#N/A,#N/A,TRUE,"Recap Mat";#N/A,#N/A,TRUE,"ING CAM-TB";#N/A,#N/A,TRUE,"ING CAM-60%";#N/A,#N/A,TRUE,"ING CAM-Cru";#N/A,#N/A,TRUE,"ING COULO -52%";#N/A,#N/A,TRUE,"Recap Ing";#N/A,#N/A,TRUE,"CHARGES";#N/A,#N/A,TRUE,"Répart_charges";#N/A,#N/A,TRUE,"ENERGIES";#N/A,#N/A,TRUE,"EFFECTIF";#N/A,#N/A,TRUE,"Synthèse";#N/A,#N/A,TRUE,"CPTE EXPLOIT";#N/A,#N/A,TRUE,"PRIX CESSION";#N/A,#N/A,TRUE,"CONTROLE"}</definedName>
     <definedName name="wrn.CLECY." hidden="1">{#N/A,#N/A,TRUE,"VOLUMES";#N/A,#N/A,TRUE,"1A-TB 240";#N/A,#N/A,TRUE,"1B-TB 250";#N/A,#N/A,TRUE,"1D-Tr 240";#N/A,#N/A,TRUE,"1E-Tr 250";#N/A,#N/A,TRUE,"1M-Tr 250 60%";#N/A,#N/A,TRUE,"5A-Cru 240";#N/A,#N/A,TRUE,"5B-Cru 250";#N/A,#N/A,TRUE,"5D-Bio 250";#N/A,#N/A,TRUE,"3B-TB 320";#N/A,#N/A,TRUE,"3C-TB 350";#N/A,#N/A,TRUE,"Sérum";#N/A,#N/A,TRUE,"Recap Mat";#N/A,#N/A,TRUE,"ING CAM-TB";#N/A,#N/A,TRUE,"ING CAM-60%";#N/A,#N/A,TRUE,"ING CAM-Cru";#N/A,#N/A,TRUE,"ING COULO -52%";#N/A,#N/A,TRUE,"Recap Ing";#N/A,#N/A,TRUE,"CHARGES";#N/A,#N/A,TRUE,"Répart_charges";#N/A,#N/A,TRUE,"ENERGIES";#N/A,#N/A,TRUE,"EFFECTIF";#N/A,#N/A,TRUE,"Synthèse";#N/A,#N/A,TRUE,"CPTE EXPLOIT";#N/A,#N/A,TRUE,"PRIX CESSION";#N/A,#N/A,TRUE,"CONTROLE"}</definedName>
     <definedName name="wrn.CNQGLOBAL." localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RODEZ";#N/A,#N/A,FALSE,"BLEU CAUSSES";#N/A,#N/A,FALSE,"BLOC PAST";#N/A,#N/A,FALSE,"PENA";#N/A,#N/A,FALSE,"BUCHES";"RONDELEBASE",#N/A,FALSE,"RONDELE";"LONS",#N/A,FALSE,"RONDELE";#N/A,#N/A,FALSE,"UHT";#N/A,#N/A,FALSE,"POUDRE LAIT";#N/A,#N/A,FALSE,"POUDRE SER"}</definedName>
+    <definedName name="wrn.CNQGLOBAL." localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RODEZ";#N/A,#N/A,FALSE,"BLEU CAUSSES";#N/A,#N/A,FALSE,"BLOC PAST";#N/A,#N/A,FALSE,"PENA";#N/A,#N/A,FALSE,"BUCHES";"RONDELEBASE",#N/A,FALSE,"RONDELE";"LONS",#N/A,FALSE,"RONDELE";#N/A,#N/A,FALSE,"UHT";#N/A,#N/A,FALSE,"POUDRE LAIT";#N/A,#N/A,FALSE,"POUDRE SER"}</definedName>
     <definedName name="wrn.CNQGLOBAL." hidden="1">{#N/A,#N/A,FALSE,"RODEZ";#N/A,#N/A,FALSE,"BLEU CAUSSES";#N/A,#N/A,FALSE,"BLOC PAST";#N/A,#N/A,FALSE,"PENA";#N/A,#N/A,FALSE,"BUCHES";"RONDELEBASE",#N/A,FALSE,"RONDELE";"LONS",#N/A,FALSE,"RONDELE";#N/A,#N/A,FALSE,"UHT";#N/A,#N/A,FALSE,"POUDRE LAIT";#N/A,#N/A,FALSE,"POUDRE SER"}</definedName>
     <definedName name="wrn.COMMENTAIRES." localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"EC COMM-c";#N/A,#N/A,FALSE,"EC PAR PDTS-c";#N/A,#N/A,FALSE,"EC MAT-c";#N/A,#N/A,FALSE,"SUIVI HAUSSES-c"}</definedName>
+    <definedName name="wrn.COMMENTAIRES." localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"EC COMM-c";#N/A,#N/A,FALSE,"EC PAR PDTS-c";#N/A,#N/A,FALSE,"EC MAT-c";#N/A,#N/A,FALSE,"SUIVI HAUSSES-c"}</definedName>
     <definedName name="wrn.COMMENTAIRES." hidden="1">{#N/A,#N/A,FALSE,"EC COMM-c";#N/A,#N/A,FALSE,"EC PAR PDTS-c";#N/A,#N/A,FALSE,"EC MAT-c";#N/A,#N/A,FALSE,"SUIVI HAUSSES-c"}</definedName>
     <definedName name="wrn.Complet." localSheetId="0" hidden="1">{"fr_collecte",#N/A,FALSE,"Fr_SA";"Fr_holding",#N/A,FALSE,"Fr_SA";"Frais_from",#N/A,FALSE,"Frs";"Couverture",#N/A,FALSE,"Frs";"Activité",#N/A,FALSE,"Act";"Act_commentaires",#N/A,FALSE,"Act";"Eff_personnel",#N/A,FALSE,"Eff";"Rendement",#N/A,FALSE,"Rdt";"Péreq",#N/A,FALSE,"Péreq";"récapit_mat",#N/A,FALSE,"récap_matière";#N/A,#N/A,FALSE,"Pci";"Ing_ingrédients",#N/A,FALSE,"Ing";"pci_évolution",#N/A,FALSE,"Pci";"pci_CA",#N/A,FALSE,"Pci";"pci_amélioration",#N/A,FALSE,"Pci";"SIG_Vercel",#N/A,FALSE,"Pci";"SIG_Philipona",#N/A,FALSE,"Pci"}</definedName>
+    <definedName name="wrn.Complet." localSheetId="1" hidden="1">{"fr_collecte",#N/A,FALSE,"Fr_SA";"Fr_holding",#N/A,FALSE,"Fr_SA";"Frais_from",#N/A,FALSE,"Frs";"Couverture",#N/A,FALSE,"Frs";"Activité",#N/A,FALSE,"Act";"Act_commentaires",#N/A,FALSE,"Act";"Eff_personnel",#N/A,FALSE,"Eff";"Rendement",#N/A,FALSE,"Rdt";"Péreq",#N/A,FALSE,"Péreq";"récapit_mat",#N/A,FALSE,"récap_matière";#N/A,#N/A,FALSE,"Pci";"Ing_ingrédients",#N/A,FALSE,"Ing";"pci_évolution",#N/A,FALSE,"Pci";"pci_CA",#N/A,FALSE,"Pci";"pci_amélioration",#N/A,FALSE,"Pci";"SIG_Vercel",#N/A,FALSE,"Pci";"SIG_Philipona",#N/A,FALSE,"Pci"}</definedName>
     <definedName name="wrn.Complet." hidden="1">{"fr_collecte",#N/A,FALSE,"Fr_SA";"Fr_holding",#N/A,FALSE,"Fr_SA";"Frais_from",#N/A,FALSE,"Frs";"Couverture",#N/A,FALSE,"Frs";"Activité",#N/A,FALSE,"Act";"Act_commentaires",#N/A,FALSE,"Act";"Eff_personnel",#N/A,FALSE,"Eff";"Rendement",#N/A,FALSE,"Rdt";"Péreq",#N/A,FALSE,"Péreq";"récapit_mat",#N/A,FALSE,"récap_matière";#N/A,#N/A,FALSE,"Pci";"Ing_ingrédients",#N/A,FALSE,"Ing";"pci_évolution",#N/A,FALSE,"Pci";"pci_CA",#N/A,FALSE,"Pci";"pci_amélioration",#N/A,FALSE,"Pci";"SIG_Vercel",#N/A,FALSE,"Pci";"SIG_Philipona",#N/A,FALSE,"Pci"}</definedName>
     <definedName name="wrn.CUMUL." localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge"}</definedName>
+    <definedName name="wrn.CUMUL." localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge"}</definedName>
     <definedName name="wrn.CUMUL." hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge"}</definedName>
     <definedName name="wrn.EDITION." localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"VOLUMES";#N/A,#N/A,TRUE,"RDT CAM";#N/A,#N/A,TRUE,"RDT BDP";#N/A,#N/A,TRUE,"RDT LIV250";#N/A,#N/A,TRUE,"RDT LIV500";#N/A,#N/A,TRUE,"ING CAM";#N/A,#N/A,TRUE,"ING BDP";#N/A,#N/A,TRUE,"ING LIV";#N/A,#N/A,TRUE,"CHARGES";#N/A,#N/A,TRUE,"ENERGIES";#N/A,#N/A,TRUE,"PRODCHIM";#N/A,#N/A,TRUE,"EFFECTIF";#N/A,#N/A,TRUE,"PRIX CESSION";#N/A,#N/A,TRUE,"CPTE EXPLOIT";#N/A,#N/A,TRUE,"CONTROLE"}</definedName>
+    <definedName name="wrn.EDITION." localSheetId="1" hidden="1">{#N/A,#N/A,TRUE,"VOLUMES";#N/A,#N/A,TRUE,"RDT CAM";#N/A,#N/A,TRUE,"RDT BDP";#N/A,#N/A,TRUE,"RDT LIV250";#N/A,#N/A,TRUE,"RDT LIV500";#N/A,#N/A,TRUE,"ING CAM";#N/A,#N/A,TRUE,"ING BDP";#N/A,#N/A,TRUE,"ING LIV";#N/A,#N/A,TRUE,"CHARGES";#N/A,#N/A,TRUE,"ENERGIES";#N/A,#N/A,TRUE,"PRODCHIM";#N/A,#N/A,TRUE,"EFFECTIF";#N/A,#N/A,TRUE,"PRIX CESSION";#N/A,#N/A,TRUE,"CPTE EXPLOIT";#N/A,#N/A,TRUE,"CONTROLE"}</definedName>
     <definedName name="wrn.EDITION." hidden="1">{#N/A,#N/A,TRUE,"VOLUMES";#N/A,#N/A,TRUE,"RDT CAM";#N/A,#N/A,TRUE,"RDT BDP";#N/A,#N/A,TRUE,"RDT LIV250";#N/A,#N/A,TRUE,"RDT LIV500";#N/A,#N/A,TRUE,"ING CAM";#N/A,#N/A,TRUE,"ING BDP";#N/A,#N/A,TRUE,"ING LIV";#N/A,#N/A,TRUE,"CHARGES";#N/A,#N/A,TRUE,"ENERGIES";#N/A,#N/A,TRUE,"PRODCHIM";#N/A,#N/A,TRUE,"EFFECTIF";#N/A,#N/A,TRUE,"PRIX CESSION";#N/A,#N/A,TRUE,"CPTE EXPLOIT";#N/A,#N/A,TRUE,"CONTROLE"}</definedName>
     <definedName name="wrn.ex." localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ANALYSE";#N/A,#N/A,FALSE,"PM VALEUR"}</definedName>
+    <definedName name="wrn.ex." localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ANALYSE";#N/A,#N/A,FALSE,"PM VALEUR"}</definedName>
     <definedName name="wrn.ex." hidden="1">{#N/A,#N/A,FALSE,"ANALYSE";#N/A,#N/A,FALSE,"PM VALEUR"}</definedName>
     <definedName name="wrn.Impression._.totale." localSheetId="0" hidden="1">{"Analyse charges",#N/A,FALSE,"Feuil1 (2)";"Ratios activités",#N/A,FALSE,"Feuil1 (2)";"Indicateurs",#N/A,FALSE,"Feuil1 (2)"}</definedName>
+    <definedName name="wrn.Impression._.totale." localSheetId="1" hidden="1">{"Analyse charges",#N/A,FALSE,"Feuil1 (2)";"Ratios activités",#N/A,FALSE,"Feuil1 (2)";"Indicateurs",#N/A,FALSE,"Feuil1 (2)"}</definedName>
     <definedName name="wrn.Impression._.totale." hidden="1">{"Analyse charges",#N/A,FALSE,"Feuil1 (2)";"Ratios activités",#N/A,FALSE,"Feuil1 (2)";"Indicateurs",#N/A,FALSE,"Feuil1 (2)"}</definedName>
     <definedName name="wrn.Indicateurs." localSheetId="0" hidden="1">{"Indicateurs",#N/A,FALSE,"Feuil1 (2)"}</definedName>
+    <definedName name="wrn.Indicateurs." localSheetId="1" hidden="1">{"Indicateurs",#N/A,FALSE,"Feuil1 (2)"}</definedName>
     <definedName name="wrn.Indicateurs." hidden="1">{"Indicateurs",#N/A,FALSE,"Feuil1 (2)"}</definedName>
     <definedName name="wrn.MENSUEL." localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge";#N/A,#N/A,FALSE,"cumul I";#N/A,#N/A,FALSE,"cumul II";#N/A,#N/A,FALSE,"cumul III"}</definedName>
+    <definedName name="wrn.MENSUEL." localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge";#N/A,#N/A,FALSE,"cumul I";#N/A,#N/A,FALSE,"cumul II";#N/A,#N/A,FALSE,"cumul III"}</definedName>
     <definedName name="wrn.MENSUEL." hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge";#N/A,#N/A,FALSE,"cumul I";#N/A,#N/A,FALSE,"cumul II";#N/A,#N/A,FALSE,"cumul III"}</definedName>
     <definedName name="wrn.MOYENNE." localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge"}</definedName>
+    <definedName name="wrn.MOYENNE." localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge"}</definedName>
     <definedName name="wrn.MOYENNE." hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge"}</definedName>
     <definedName name="wrn.novgl." localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="wrn.novgl." localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="wrn.novgl." hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="wrn.Ratios." localSheetId="0" hidden="1">{"Ratios activités",#N/A,FALSE,"Feuil1 (2)"}</definedName>
+    <definedName name="wrn.Ratios." localSheetId="1" hidden="1">{"Ratios activités",#N/A,FALSE,"Feuil1 (2)"}</definedName>
     <definedName name="wrn.Ratios." hidden="1">{"Ratios activités",#N/A,FALSE,"Feuil1 (2)"}</definedName>
     <definedName name="wrn.REELBUD." localSheetId="0" hidden="1">{"DETAIL",#N/A,FALSE,"REELBUDGET";"TOTAL",#N/A,FALSE,"REELBUDGET"}</definedName>
+    <definedName name="wrn.REELBUD." localSheetId="1" hidden="1">{"DETAIL",#N/A,FALSE,"REELBUDGET";"TOTAL",#N/A,FALSE,"REELBUDGET"}</definedName>
     <definedName name="wrn.REELBUD." hidden="1">{"DETAIL",#N/A,FALSE,"REELBUDGET";"TOTAL",#N/A,FALSE,"REELBUDGET"}</definedName>
     <definedName name="wrn.Résultat." localSheetId="0" hidden="1">{"Struct",#N/A,FALSE,"Récap Struct";"Struct",#N/A,FALSE,"Récap Struct";"Chges Total",#N/A,FALSE,"Chges Récap";"Chges Détail",#N/A,FALSE,"Chges Récap";"Struct",#N/A,FALSE,"Récap Struct";"Chges Total",#N/A,FALSE,"Chges Récap";"Chges Détail",#N/A,FALSE,"Chges Récap";"Détail",#N/A,FALSE,"Chges Détail"}</definedName>
+    <definedName name="wrn.Résultat." localSheetId="1" hidden="1">{"Struct",#N/A,FALSE,"Récap Struct";"Struct",#N/A,FALSE,"Récap Struct";"Chges Total",#N/A,FALSE,"Chges Récap";"Chges Détail",#N/A,FALSE,"Chges Récap";"Struct",#N/A,FALSE,"Récap Struct";"Chges Total",#N/A,FALSE,"Chges Récap";"Chges Détail",#N/A,FALSE,"Chges Récap";"Détail",#N/A,FALSE,"Chges Détail"}</definedName>
     <definedName name="wrn.Résultat." hidden="1">{"Struct",#N/A,FALSE,"Récap Struct";"Struct",#N/A,FALSE,"Récap Struct";"Chges Total",#N/A,FALSE,"Chges Récap";"Chges Détail",#N/A,FALSE,"Chges Récap";"Struct",#N/A,FALSE,"Récap Struct";"Chges Total",#N/A,FALSE,"Chges Récap";"Chges Détail",#N/A,FALSE,"Chges Récap";"Détail",#N/A,FALSE,"Chges Détail"}</definedName>
     <definedName name="wrn.SPA1." localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="wrn.SPA1." localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wrn.SPA1." hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wrn.SPM1." localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="wrn.SPM1." localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wrn.SPM1." hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wrn.SYNTHESE." localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"ANALYSE";#N/A,#N/A,TRUE,"PM VOLUME";#N/A,#N/A,TRUE,"PM VALEUR";#N/A,#N/A,TRUE,"AR1";#N/A,#N/A,TRUE,"AR2";#N/A,#N/A,TRUE,"RAF";#N/A,#N/A,TRUE,"BILAN";#N/A,#N/A,TRUE,"CASH FLOW";#N/A,#N/A,TRUE,"ETAT FI"}</definedName>
+    <definedName name="wrn.SYNTHESE." localSheetId="1" hidden="1">{#N/A,#N/A,TRUE,"ANALYSE";#N/A,#N/A,TRUE,"PM VOLUME";#N/A,#N/A,TRUE,"PM VALEUR";#N/A,#N/A,TRUE,"AR1";#N/A,#N/A,TRUE,"AR2";#N/A,#N/A,TRUE,"RAF";#N/A,#N/A,TRUE,"BILAN";#N/A,#N/A,TRUE,"CASH FLOW";#N/A,#N/A,TRUE,"ETAT FI"}</definedName>
     <definedName name="wrn.SYNTHESE." hidden="1">{#N/A,#N/A,TRUE,"ANALYSE";#N/A,#N/A,TRUE,"PM VOLUME";#N/A,#N/A,TRUE,"PM VALEUR";#N/A,#N/A,TRUE,"AR1";#N/A,#N/A,TRUE,"AR2";#N/A,#N/A,TRUE,"RAF";#N/A,#N/A,TRUE,"BILAN";#N/A,#N/A,TRUE,"CASH FLOW";#N/A,#N/A,TRUE,"ETAT FI"}</definedName>
     <definedName name="wrn.TABLEAUX." localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"EC COMM-t";#N/A,#N/A,TRUE,"EC PAR PDTS-t";#N/A,#N/A,TRUE,"EC MAT-t";#N/A,#N/A,TRUE,"SUIVI HAUSSES-t"}</definedName>
+    <definedName name="wrn.TABLEAUX." localSheetId="1" hidden="1">{#N/A,#N/A,TRUE,"EC COMM-t";#N/A,#N/A,TRUE,"EC PAR PDTS-t";#N/A,#N/A,TRUE,"EC MAT-t";#N/A,#N/A,TRUE,"SUIVI HAUSSES-t"}</definedName>
     <definedName name="wrn.TABLEAUX." hidden="1">{#N/A,#N/A,TRUE,"EC COMM-t";#N/A,#N/A,TRUE,"EC PAR PDTS-t";#N/A,#N/A,TRUE,"EC MAT-t";#N/A,#N/A,TRUE,"SUIVI HAUSSES-t"}</definedName>
     <definedName name="wrn1.CCC." localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="wrn1.CCC." localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wrn1.CCC." hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wwww" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="wwww" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wwww" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wwwwww" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="wwwwww" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="wwwwww" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="wwwwwwwwwwww" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="wwwwwwwwwwww" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wwwwwwwwwwww" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ybukkbyitkituk" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="ybukkbyitkituk" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ybukkbyitkituk" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="yertyyyy" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="yertyyyy" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="yertyyyy" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="yeyyyy" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="yeyyyy" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="yeyyyy" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="yrnukuilky8u" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="yrnukuilky8u" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="yrnukuilky8u" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="YY" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="YY" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="YY" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="yyqeyqy" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="yyqeyqy" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="yyqeyqy" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="yyyyy" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="yyyyy" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="yyyyy" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="yyyyyy" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="yyyyyy" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="yyyyyy" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="zefzaefze" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="zefzaefze" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="zefzaefze" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="zefzerfzef" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="zefzerfzef" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="zefzerfzef" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="zegtrgzgt" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="zegtrgzgt" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="zegtrgzgt" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="zz" hidden="1">#REF!</definedName>
     <definedName name="zzfzafz" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="zzfzafz" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="zzfzafz" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="zzz" hidden="1">#REF!</definedName>
     <definedName name="zzzzz" hidden="1">#REF!</definedName>
     <definedName name="zzzzzz" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="zzzzzz" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="zzzzzz" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="zzzzzzz" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
+    <definedName name="zzzzzzz" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="zzzzzzz" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="zzzzzzzzzz" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="zzzzzzzzzz" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="zzzzzzzzzz" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="zzzzzzzzzzzzz" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="zzzzzzzzzzzzz" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="zzzzzzzzzzzzz" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="zzzzzzzzzzzzzz" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="zzzzzzzzzzzzzz" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="zzzzzzzzzzzzzz" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="zzzzzzzzzzzzzzzzzz" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
+    <definedName name="zzzzzzzzzzzzzzzzzz" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="zzzzzzzzzzzzzzzzzz" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -734,7 +961,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="62">
   <si>
     <t>Total</t>
   </si>
@@ -914,6 +1141,12 @@
   </si>
   <si>
     <t>Consumo por kg</t>
+  </si>
+  <si>
+    <t>Real error análisis</t>
+  </si>
+  <si>
+    <t>errores analíticos</t>
   </si>
 </sst>
 </file>
@@ -959,7 +1192,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -994,6 +1227,12 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1179,7 +1418,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1284,12 +1523,22 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1309,22 +1558,6 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Estándar técnico"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1421,7 +1654,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1933,7 +2166,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1974,7 +2207,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3019,7 +3252,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3058,7 +3291,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3148,7 +3381,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3193,7 +3426,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3305,6 +3538,10 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3939,10 +4176,10 @@
       <c r="C23" s="39">
         <v>5.03</v>
       </c>
-      <c r="E23" s="70" t="s">
+      <c r="E23" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="F23" s="71"/>
+      <c r="F23" s="70"/>
       <c r="G23" s="17">
         <f>SUM(G21:G22)</f>
         <v>405.94837762824363</v>
@@ -4359,4 +4596,957 @@
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="77" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB4B7AF-4A19-43C6-8A13-3A5EBCA6F48D}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L43"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="51" customWidth="1"/>
+    <col min="2" max="4" width="13.5703125" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="16.7109375" customWidth="1"/>
+    <col min="9" max="9" width="10.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="67" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="66" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="66" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="66" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="66" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="41"/>
+      <c r="C2" s="65">
+        <v>1960</v>
+      </c>
+      <c r="E2" s="65">
+        <v>1960</v>
+      </c>
+      <c r="F2" s="65">
+        <v>1960</v>
+      </c>
+      <c r="H2" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="63">
+        <v>0.55630000000000002</v>
+      </c>
+      <c r="C3" s="62">
+        <v>0.55940000000000001</v>
+      </c>
+      <c r="E3" s="62">
+        <v>0.55940000000000001</v>
+      </c>
+      <c r="F3" s="62">
+        <v>0.55940000000000001</v>
+      </c>
+      <c r="H3" s="61" t="s">
+        <v>50</v>
+      </c>
+      <c r="I3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="59" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="50">
+        <v>0.30049999999999999</v>
+      </c>
+      <c r="C4" s="60">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="E4" s="60">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="F4" s="60">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I4" s="58" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="59" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="49">
+        <f>B3-B4</f>
+        <v>0.25580000000000003</v>
+      </c>
+      <c r="C5" s="49">
+        <f>C3-C4</f>
+        <v>0.26440000000000002</v>
+      </c>
+      <c r="E5" s="49">
+        <f>E3-E4</f>
+        <v>0.26440000000000002</v>
+      </c>
+      <c r="F5" s="49">
+        <f>F3-F4</f>
+        <v>0.26440000000000002</v>
+      </c>
+      <c r="H5" s="12"/>
+      <c r="I5" s="58"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="57">
+        <f>(1-B3)/(1-B4)</f>
+        <v>0.63431022158684769</v>
+      </c>
+      <c r="C6" s="57">
+        <f>(1-C3)/(1-C4)</f>
+        <v>0.62496453900709215</v>
+      </c>
+      <c r="E6" s="57">
+        <f>(1-E3)/(1-E4)</f>
+        <v>0.62496453900709215</v>
+      </c>
+      <c r="F6" s="57">
+        <f>(1-F3)/(1-F4)</f>
+        <v>0.62496453900709215</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="56">
+        <f>B4/B3</f>
+        <v>0.54017616394031998</v>
+      </c>
+      <c r="C7" s="56">
+        <f>C4/C3</f>
+        <v>0.52735073292813728</v>
+      </c>
+      <c r="E7" s="56">
+        <f>E4/E3</f>
+        <v>0.52735073292813728</v>
+      </c>
+      <c r="F7" s="56">
+        <f>F4/F3</f>
+        <v>0.52735073292813728</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="29"/>
+      <c r="C8" s="55">
+        <v>15350</v>
+      </c>
+      <c r="E8" s="55">
+        <v>15350</v>
+      </c>
+      <c r="F8" s="55">
+        <v>15350</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="4">
+        <f>B11*1000/C8</f>
+        <v>42.267055048788173</v>
+      </c>
+      <c r="C9" s="54">
+        <v>39.03</v>
+      </c>
+      <c r="E9" s="71">
+        <f>C9*1.025</f>
+        <v>40.005749999999999</v>
+      </c>
+      <c r="F9" s="71">
+        <f>C9*0.975</f>
+        <v>38.054250000000003</v>
+      </c>
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="4">
+        <f>B12*1000/C8</f>
+        <v>35.310713971300295</v>
+      </c>
+      <c r="C10" s="54">
+        <v>34.17</v>
+      </c>
+      <c r="E10" s="71">
+        <f>C10*0.975</f>
+        <v>33.315750000000001</v>
+      </c>
+      <c r="F10" s="71">
+        <f>C10*1.025</f>
+        <v>35.024250000000002</v>
+      </c>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="51" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="4">
+        <f>B$4/B$15*C$2</f>
+        <v>648.7992949988984</v>
+      </c>
+      <c r="C11" s="4">
+        <f>C9*C8/1000</f>
+        <v>599.1105</v>
+      </c>
+      <c r="D11" s="12"/>
+      <c r="E11" s="4">
+        <f>E9*E8/1000</f>
+        <v>614.08826249999993</v>
+      </c>
+      <c r="F11" s="4">
+        <f>F9*F8/1000</f>
+        <v>584.13273750000008</v>
+      </c>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="4">
+        <f>C$2*B$5/B$16</f>
+        <v>542.01945945945954</v>
+      </c>
+      <c r="C12" s="4">
+        <f>C10*C8/1000</f>
+        <v>524.5095</v>
+      </c>
+      <c r="D12" s="12"/>
+      <c r="E12" s="4">
+        <f>E10*E8/1000</f>
+        <v>511.39676250000002</v>
+      </c>
+      <c r="F12" s="4">
+        <f>F10*F8/1000</f>
+        <v>537.6222375000001</v>
+      </c>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="53">
+        <f>B11/B12</f>
+        <v>1.1970036936421569</v>
+      </c>
+      <c r="C13" s="53">
+        <f>C11/C12</f>
+        <v>1.1422300263388938</v>
+      </c>
+      <c r="E13" s="53">
+        <f>E11/E12</f>
+        <v>1.2008059251255034</v>
+      </c>
+      <c r="F13" s="53">
+        <f>F11/F12</f>
+        <v>1.0865114884687037</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="52">
+        <f>(B5*1000/B10)</f>
+        <v>7.2442602040816331</v>
+      </c>
+      <c r="C14" s="52">
+        <f>(C5*1000/C10)</f>
+        <v>7.7377816798361145</v>
+      </c>
+      <c r="E14" s="52">
+        <f>(E5*1000/E10)</f>
+        <v>7.9361863382934503</v>
+      </c>
+      <c r="F14" s="52">
+        <f>(F5*1000/F10)</f>
+        <v>7.5490552974010869</v>
+      </c>
+      <c r="L14" s="12"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="50">
+        <v>0.90780000000000005</v>
+      </c>
+      <c r="C15" s="49">
+        <f>C4*C2/C11</f>
+        <v>0.96509742359714934</v>
+      </c>
+      <c r="E15" s="49">
+        <f>E4*E2/E11</f>
+        <v>0.94155846204599947</v>
+      </c>
+      <c r="F15" s="49">
+        <f>F4*F2/F11</f>
+        <v>0.98984351138169147</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="50">
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="C16" s="49">
+        <f>C5*C2/C12</f>
+        <v>0.98801642296278724</v>
+      </c>
+      <c r="E16" s="49">
+        <f>E5*E2/E12</f>
+        <v>1.0133501773977305</v>
+      </c>
+      <c r="F16" s="49">
+        <f>F5*F2/F12</f>
+        <v>0.96391846142710935</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="9">
+        <f>(B4*C2)-B11</f>
+        <v>-59.819294998898386</v>
+      </c>
+      <c r="C17" s="9">
+        <f>(C4*C2)-C11</f>
+        <v>-20.91050000000007</v>
+      </c>
+      <c r="E17" s="9">
+        <f>(E4*E2)-E11</f>
+        <v>-35.888262499999996</v>
+      </c>
+      <c r="F17" s="9">
+        <f>(F4*F2)-F11</f>
+        <v>-5.9327375000001439</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="47" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="46">
+        <f>B17/B11</f>
+        <v>-9.2199999999999921E-2</v>
+      </c>
+      <c r="C18" s="45">
+        <f>C17/C11</f>
+        <v>-3.4902576402850674E-2</v>
+      </c>
+      <c r="E18" s="45">
+        <f>E17/E11</f>
+        <v>-5.8441537954000547E-2</v>
+      </c>
+      <c r="F18" s="45">
+        <f>F17/F11</f>
+        <v>-1.015648861830851E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="68"/>
+      <c r="B19" s="69"/>
+      <c r="C19" s="69"/>
+      <c r="E19" s="69"/>
+      <c r="F19" s="69"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="44"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="43">
+        <f>B11/C2*1000</f>
+        <v>331.02004846882573</v>
+      </c>
+      <c r="C21" s="43">
+        <f>C9*C8/C2</f>
+        <v>305.66862244897959</v>
+      </c>
+      <c r="E21" s="43">
+        <f>E9*E8/E2</f>
+        <v>313.31033801020408</v>
+      </c>
+      <c r="F21" s="43">
+        <f>F9*F8/F2</f>
+        <v>298.0269068877551</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="J21" s="72" t="s">
+        <v>30</v>
+      </c>
+      <c r="K21" s="73" t="s">
+        <v>61</v>
+      </c>
+      <c r="L21" s="74"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="42">
+        <f>B12/C2*1000</f>
+        <v>276.54054054054058</v>
+      </c>
+      <c r="C22" s="42">
+        <f>C10*C8/C2</f>
+        <v>267.60688775510204</v>
+      </c>
+      <c r="E22" s="42">
+        <f>E10*E8/E2</f>
+        <v>260.91671556122452</v>
+      </c>
+      <c r="F22" s="42">
+        <f>F10*F8/F2</f>
+        <v>274.29705994897961</v>
+      </c>
+      <c r="H22" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="I22" s="9">
+        <f>(B21-C21)/1000*$C$2</f>
+        <v>49.688794998898445</v>
+      </c>
+      <c r="J22" s="9">
+        <f>((B21-C21)*C2*B23/1000)</f>
+        <v>249.93463884445916</v>
+      </c>
+      <c r="K22" s="71">
+        <f>(B21-E21)*E23*E2/1000</f>
+        <v>174.5964934694592</v>
+      </c>
+      <c r="L22" s="71">
+        <f>(B21-F21)*F23*F2/1000</f>
+        <v>325.27278421945908</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="39">
+        <v>5.03</v>
+      </c>
+      <c r="C23" s="39">
+        <v>5.03</v>
+      </c>
+      <c r="E23" s="39">
+        <v>5.03</v>
+      </c>
+      <c r="F23" s="39">
+        <v>5.03</v>
+      </c>
+      <c r="H23" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" s="1">
+        <f>(B22-C22)/1000*$C$2</f>
+        <v>17.509959459459537</v>
+      </c>
+      <c r="J23" s="1">
+        <f>((B22-C22)*C2*B24/1000)</f>
+        <v>156.01373878378448</v>
+      </c>
+      <c r="K23" s="75">
+        <f>(B22-E22)*E24*E2/1000</f>
+        <v>272.84822990878388</v>
+      </c>
+      <c r="L23" s="75">
+        <f>(B22-F22)*F24*F2/1000</f>
+        <v>39.179247658784107</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="36">
+        <v>8.91</v>
+      </c>
+      <c r="C24" s="36">
+        <v>8.91</v>
+      </c>
+      <c r="E24" s="36">
+        <v>8.91</v>
+      </c>
+      <c r="F24" s="36">
+        <v>8.91</v>
+      </c>
+      <c r="H24" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="17">
+        <f>SUM(J22:J23)</f>
+        <v>405.94837762824363</v>
+      </c>
+      <c r="K24" s="17">
+        <f t="shared" ref="K24:L24" si="0">SUM(K22:K23)</f>
+        <v>447.44472337824311</v>
+      </c>
+      <c r="L24" s="17">
+        <f t="shared" si="0"/>
+        <v>364.45203187824319</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="35"/>
+      <c r="B25" s="34"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="12"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B27" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="I27" s="32" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="28"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="17">
+        <f>C$2*B$4/B$15</f>
+        <v>648.7992949988984</v>
+      </c>
+      <c r="C29" s="17">
+        <f>$C$2*$C$4/$C$15</f>
+        <v>599.1105</v>
+      </c>
+      <c r="D29" s="16">
+        <f>B29-C29</f>
+        <v>49.688794998898402</v>
+      </c>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="16"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="4">
+        <f>C$2*B$4/B$15</f>
+        <v>648.7992949988984</v>
+      </c>
+      <c r="C30" s="4">
+        <f>$C$2*$C$4/$B$15</f>
+        <v>636.92443269442595</v>
+      </c>
+      <c r="D30" s="23">
+        <f>B30-C30</f>
+        <v>11.874862304472458</v>
+      </c>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24">
+        <f>D30</f>
+        <v>11.874862304472458</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4">
+        <f>F30*B$23</f>
+        <v>59.730557391496468</v>
+      </c>
+      <c r="I30" s="23">
+        <f>SUM(G30:H30)</f>
+        <v>59.730557391496468</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="4">
+        <f>C$2*B$4/B$15</f>
+        <v>648.7992949988984</v>
+      </c>
+      <c r="C31" s="4">
+        <f>$C$2*$B$4/$C$15</f>
+        <v>610.28035677966113</v>
+      </c>
+      <c r="D31" s="23">
+        <f>B31-C31</f>
+        <v>38.51893821923727</v>
+      </c>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24">
+        <f>D31</f>
+        <v>38.51893821923727</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4">
+        <f>F31*B$23</f>
+        <v>193.75025924276349</v>
+      </c>
+      <c r="I31" s="23">
+        <f>SUM(G31:H31)</f>
+        <v>193.75025924276349</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="6">
+        <f>(B15-C15)*(B4-C4)*C2</f>
+        <v>-0.61766622637726987</v>
+      </c>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21">
+        <f>D32</f>
+        <v>-0.61766622637726987</v>
+      </c>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1">
+        <f>F32*B$23</f>
+        <v>-3.1068611186776676</v>
+      </c>
+      <c r="I32" s="6">
+        <f>SUM(G32:H32)</f>
+        <v>-3.1068611186776676</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" s="17">
+        <f>C$2*B$5/B$16</f>
+        <v>542.01945945945954</v>
+      </c>
+      <c r="C33" s="17">
+        <f>$C$2*$C$5/$C$16</f>
+        <v>524.5095</v>
+      </c>
+      <c r="D33" s="16">
+        <f>B33-C33</f>
+        <v>17.509959459459537</v>
+      </c>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="16"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" s="4">
+        <f>C$2*B$5/B$16</f>
+        <v>542.01945945945954</v>
+      </c>
+      <c r="C34" s="4">
+        <f>C2*C5/B16</f>
+        <v>560.24216216216223</v>
+      </c>
+      <c r="D34" s="23">
+        <f>B34-C34</f>
+        <v>-18.222702702702691</v>
+      </c>
+      <c r="E34" s="24">
+        <f>D34</f>
+        <v>-18.222702702702691</v>
+      </c>
+      <c r="F34" s="24"/>
+      <c r="G34" s="4">
+        <f>E34*B$24</f>
+        <v>-162.36428108108097</v>
+      </c>
+      <c r="H34" s="4"/>
+      <c r="I34" s="23">
+        <f>SUM(G34:H34)</f>
+        <v>-162.36428108108097</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" s="4">
+        <f>C$2*B$5/B$16</f>
+        <v>542.01945945945954</v>
+      </c>
+      <c r="C35" s="4">
+        <f>C2*B5/C16</f>
+        <v>507.44905484114975</v>
+      </c>
+      <c r="D35" s="23">
+        <f>B35-C35</f>
+        <v>34.570404618309794</v>
+      </c>
+      <c r="E35" s="24">
+        <f>D35</f>
+        <v>34.570404618309794</v>
+      </c>
+      <c r="F35" s="24"/>
+      <c r="G35" s="4">
+        <f>E35*B$24</f>
+        <v>308.02230514914027</v>
+      </c>
+      <c r="H35" s="4"/>
+      <c r="I35" s="23">
+        <f>SUM(G35:H35)</f>
+        <v>308.02230514914027</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="1">
+        <f>(B16-C16)*(B5-C5)*C2</f>
+        <v>1.0622048254607406</v>
+      </c>
+      <c r="E36" s="21">
+        <f>D36</f>
+        <v>1.0622048254607406</v>
+      </c>
+      <c r="F36" s="21"/>
+      <c r="G36" s="1">
+        <f>E36*B$24</f>
+        <v>9.4642449948551981</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="6">
+        <f>SUM(G36:H36)</f>
+        <v>9.4642449948551981</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="17"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="18">
+        <f>SUM(E29:E36)</f>
+        <v>17.409906741067843</v>
+      </c>
+      <c r="F37" s="18">
+        <f>SUM(F29:F36)</f>
+        <v>49.776134297332462</v>
+      </c>
+      <c r="G37" s="17">
+        <f>SUM(G29:G36)</f>
+        <v>155.12226906291448</v>
+      </c>
+      <c r="H37" s="17">
+        <f>SUM(H29:H36)</f>
+        <v>250.37395551558228</v>
+      </c>
+      <c r="I37" s="16">
+        <f>SUM(I29:I36)</f>
+        <v>405.49622457849682</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" s="14"/>
+      <c r="F39" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="H39" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="I39" s="13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B40" s="9">
+        <f>SUM(I30,I34)</f>
+        <v>-102.63372368958451</v>
+      </c>
+      <c r="D40" s="12"/>
+      <c r="E40" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F40" s="9">
+        <f>B11</f>
+        <v>648.7992949988984</v>
+      </c>
+      <c r="G40" s="10">
+        <f>C11</f>
+        <v>599.1105</v>
+      </c>
+      <c r="H40" s="9">
+        <f>F40-G40</f>
+        <v>49.688794998898402</v>
+      </c>
+      <c r="I40" s="8">
+        <f>H40*B23</f>
+        <v>249.93463884445899</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B41" s="4">
+        <f>SUM(I31,I35)</f>
+        <v>501.77256439190376</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F41" s="1">
+        <f>B12</f>
+        <v>542.01945945945954</v>
+      </c>
+      <c r="G41" s="7">
+        <f>C12</f>
+        <v>524.5095</v>
+      </c>
+      <c r="H41" s="1">
+        <f>F41-G41</f>
+        <v>17.509959459459537</v>
+      </c>
+      <c r="I41" s="6">
+        <f>H41*B24</f>
+        <v>156.01373878378448</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B42" s="4">
+        <f>SUM(I32+I36)</f>
+        <v>6.357383876177531</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="F42" s="19"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="17">
+        <f>SUM(I40:I41)</f>
+        <v>405.94837762824346</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="1">
+        <f>SUM(B40:B42)</f>
+        <v>405.49622457849682</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="77" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>